--- a/sample_data/수집일지_샘플2.xlsx
+++ b/sample_data/수집일지_샘플2.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,770 +456,743 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10006</v>
+        <v>10001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P-0016</t>
+          <t>P-0011</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>12340006</t>
+          <t>12340001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>강카타</t>
+          <t>김가나</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>F55.12</t>
+          <t>M93.05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20010</v>
+        <v>10002</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P-0110</t>
+          <t>P-0012</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>12340010</t>
+          <t>12340002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>임도영</t>
+          <t>이다라</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>M71.03</t>
+          <t>F75.11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10014</v>
+        <v>10003</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F-0141</t>
+          <t>P-0033</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>12340014</t>
+          <t>12340003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>나도현</t>
+          <t>박마바</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M77.07</t>
+          <t>M82.07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10014</v>
+        <v>10004</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F-0142</t>
+          <t>P-0014</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>12340014</t>
+          <t>12340004</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>나도현 배우자</t>
+          <t>최사아</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>F79.02</t>
+          <t>F90.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10008</v>
+        <v>10005</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P-0018</t>
+          <t>F-0051</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>12340008</t>
+          <t>1234005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>윤거너</t>
+          <t>정자차</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M93.02</t>
+          <t>M01.09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10024</v>
+        <v>20006</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P-0124</t>
+          <t>P-0016</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>12340024</t>
+          <t>12340006</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>신하갸</t>
+          <t>강카타</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>F87.01</t>
+          <t>F55.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10025</v>
+        <v>20006</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P-0125</t>
+          <t>P-0016</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1234025</t>
+          <t>12340006</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>구사라</t>
+          <t>강카타</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>F95.07</t>
+          <t>F55.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10026</v>
+        <v>10007</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P-0126</t>
+          <t>P-0017</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>12340026</t>
+          <t>12340007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>마아바</t>
+          <t>조파하</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>M89.02</t>
+          <t>M79.06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10027</v>
+        <v>10008</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P-0127</t>
+          <t>P-0018</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>12340027</t>
+          <t>12340008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>라나다</t>
+          <t>윤거너</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>F73.05</t>
+          <t>M93.02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10028</v>
+        <v>20010</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P-0128</t>
+          <t>P-0110</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>12340028</t>
+          <t>12340010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>하가나</t>
+          <t>임도영</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>M86.10</t>
+          <t>M71.03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10029</v>
+        <v>20010</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P-0129</t>
+          <t>P-0110</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>12340029</t>
+          <t>12340010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>자바사</t>
+          <t>임도영</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>F94.12</t>
+          <t>M71.03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10030</v>
+        <v>10014</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P-0130</t>
+          <t>F-0141</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>12340030</t>
+          <t>12340014</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>카나다</t>
+          <t>나도현</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>M78.04</t>
+          <t>M77.07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10031</v>
+        <v>10014</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P-0131</t>
+          <t>F-0141</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>12340031</t>
+          <t>12340014</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>가나다라</t>
+          <t>나도현</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>F80.07</t>
+          <t>M77.07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10031</v>
+        <v>10014</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>F-0311</t>
+          <t>F-0142</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>12340031</t>
+          <t>12340014</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>태아</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>나도현 부인</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>F79.02</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10032</v>
+        <v>10015</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P-0132</t>
+          <t>P-0115</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>12340032</t>
+          <t>1234015</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>나라마</t>
+          <t>백승호</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>M95.03</t>
+          <t>M90.04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10033</v>
+        <v>10015</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P-0133</t>
+          <t>P-0115</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>12340033</t>
+          <t>1234015</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>다라바</t>
+          <t>백승호</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>F77.09</t>
+          <t>M90.04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10034</v>
+        <v>10016</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P-0134</t>
+          <t>P-0116</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>12340034</t>
+          <t>12340016</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>라마사</t>
+          <t>신오라</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>M83.06</t>
+          <t>F84.09</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10035</v>
+        <v>10016</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P-0135</t>
+          <t>P-0116</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>12340035</t>
+          <t>12340016</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>마바아</t>
+          <t>신오라</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>F69.11</t>
+          <t>F84.09</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10036</v>
+        <v>10017</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P-0136</t>
+          <t>P-0117</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>12340036</t>
+          <t>12340017</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>바사자</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>M91.08</t>
-        </is>
-      </c>
+          <t>천도나</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10037</v>
+        <v>10018</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P-0137</t>
+          <t>P-0118</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>12340037</t>
+          <t>12340018</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>사아차</t>
+          <t>황라마</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>F86.04</t>
+          <t>M88.03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10038</v>
+        <v>10018</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P-0138</t>
+          <t>P-0118</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>12340038</t>
+          <t>12340018</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>아자카</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>황라마</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>M88.03</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10039</v>
+        <v>10019</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>P-0139</t>
+          <t>P-0119</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>12340039</t>
+          <t>12340019</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>자차카</t>
+          <t>변바사</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>F72.10</t>
+          <t>F91.06</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10040</v>
+        <v>10019</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P-0140</t>
+          <t>F-0191</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>12340040</t>
+          <t>12340019</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>차카타</t>
+          <t>뇌사자</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>M88.05</t>
+          <t>M89.10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10041</v>
+        <v>10020</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P-0141</t>
+          <t>P-0120</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>12340041</t>
+          <t>12340020</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>카타파</t>
+          <t>오아자</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>F96.02</t>
+          <t>M76.11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>10042</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>P-0142</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>12340042</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>타파하</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>M84.07</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sample_data/수집일지_샘플2.xlsx
+++ b/sample_data/수집일지_샘플2.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M01.09</t>
+          <t>F01.09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
